--- a/data_src/xlsx表/道具表.xlsx
+++ b/data_src/xlsx表/道具表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,32 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>desc</t>
+          <t>stacklimit</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>stacklimit</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>icon</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>modelicon</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
           <t>tradable</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>equipslot</t>
         </is>
       </c>
     </row>
@@ -471,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,80 +461,59 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>全局唯一数字编号</t>
+          <t>道具id</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>道具显示名</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>类型：1普通专辑/2签售专/3小卡/4娃孙/5潮牌/6活动解锁道具/22饭圈积分/23星星/24情报点</t>
+          <t>活动类型</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>道具描述</t>
+          <t>堆叠上限</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>单格叠加上限；-1=无限</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>art/icons 静态帧 id</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>art/model 模型 id（预留）</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0/1 是否可进中转站</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>空=不可穿戴；填娃孙/小卡/潮牌</t>
-        </is>
+          <t>可交易</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>教程普通专辑</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>99</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data_src/xlsx表/道具表.xlsx
+++ b/data_src/xlsx表/道具表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,25 @@
         <v>99</v>
       </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>普通专辑</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>99</v>
+      </c>
+      <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>
